--- a/experiment/Omni_bestx4/Test/results_table.xlsx
+++ b/experiment/Omni_bestx4/Test/results_table.xlsx
@@ -570,38 +570,38 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>32.099/
-0.8917</t>
+          <t>32.182/
+0.8935</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>28.611/
-0.7811</t>
+          <t>28.597/
+0.7826</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>27.554/
-0.7358</t>
+          <t>27.589/
+0.7382</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>26.023/
-0.7825</t>
+          <t>26.168/
+0.7887</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>30.336/
-0.9059</t>
+          <t>30.470/
+0.9091</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>28.925/
-0.8194</t>
+          <t>29.001/
+0.8224</t>
         </is>
       </c>
     </row>
